--- a/customer_service_forms/025_subscriber_survey--customer_service_forms.xlsx
+++ b/customer_service_forms/025_subscriber_survey--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_questions</t>
+          <t>customer_feedback</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey questions</t>
+          <t>1. What do you think about our service?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>quality_service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>2. How would you rate our service?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,99 +571,99 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact info</t>
+          <t>3. What is your contact information?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>contact_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>4. When would you like to contact us?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>contact_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>5. What time of day do you prefer to contact us?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>source_contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>6. How did you hear about us?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>7. Do you have any suggestions for us?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>changes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>8. What would you like to see changed?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>improvements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>9. How can we improve our service?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>10. Do you have any other comments?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>emotional_experience</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>11. How did you feel about our service?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>future_visit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>12. Do you plan to come back?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +827,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>quality_service_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>contact_info_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Online search</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>source_contact_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>improvements_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>faster</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>Faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>improvements_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>more_frequent</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>More frequent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>improvements_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>better_communication</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Better communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>improvements_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>emotional_experience_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>emotional_experience_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>emotional_experience_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
